--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2019_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2019_T2_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="50">
   <si>
     <t/>
   </si>
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>82</t>
+    <t>78</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.305</t>
+    <t>0.321</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>0.487</t>
+  </si>
+  <si>
+    <t>(0.057)</t>
+  </si>
+  <si>
+    <t>0.282</t>
   </si>
   <si>
     <t>(0.051)</t>
   </si>
   <si>
-    <t>0.463</t>
-  </si>
-  <si>
-    <t>(0.055)</t>
-  </si>
-  <si>
-    <t>0.268</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>0.927</t>
-  </si>
-  <si>
-    <t>(0.298)</t>
-  </si>
-  <si>
-    <t>1.134</t>
-  </si>
-  <si>
-    <t>(0.181)</t>
-  </si>
-  <si>
-    <t>0.390</t>
-  </si>
-  <si>
-    <t>(0.086)</t>
+    <t>0.974</t>
+  </si>
+  <si>
+    <t>(0.312)</t>
+  </si>
+  <si>
+    <t>1.192</t>
+  </si>
+  <si>
+    <t>(0.188)</t>
+  </si>
+  <si>
+    <t>0.410</t>
+  </si>
+  <si>
+    <t>(0.090)</t>
   </si>
   <si>
     <t>32</t>
@@ -105,9 +105,6 @@
     <t>0.500</t>
   </si>
   <si>
-    <t>(0.090)</t>
-  </si>
-  <si>
     <t>0.812</t>
   </si>
   <si>
@@ -138,7 +135,7 @@
     <t>(0.286)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +147,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.195*</t>
-  </si>
-  <si>
-    <t>0.349***</t>
-  </si>
-  <si>
-    <t>0.450***</t>
-  </si>
-  <si>
-    <t>1.198</t>
-  </si>
-  <si>
-    <t>2.303***</t>
-  </si>
-  <si>
-    <t>1.297***</t>
+    <t>0.179*</t>
+  </si>
+  <si>
+    <t>0.325***</t>
+  </si>
+  <si>
+    <t>0.437***</t>
+  </si>
+  <si>
+    <t>1.151</t>
+  </si>
+  <si>
+    <t>2.245***</t>
+  </si>
+  <si>
+    <t>1.277***</t>
   </si>
 </sst>
 </file>
@@ -232,7 +229,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
@@ -255,7 +252,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -278,7 +275,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -298,10 +295,10 @@
         <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -318,7 +315,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -341,13 +338,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -364,7 +361,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -387,13 +384,13 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -410,7 +407,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -433,13 +430,13 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -456,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -479,13 +476,13 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -502,7 +499,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -525,13 +522,13 @@
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -548,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
